--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/06_Primeiro_Turno_Media_Harmonizada_Cenarios.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/06_Primeiro_Turno_Media_Harmonizada_Cenarios.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3899,6 +3899,116 @@
       </c>
       <c r="F157" t="n">
         <v>0.1943154664693951</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>35.43047169119026</v>
+      </c>
+      <c r="D158" t="n">
+        <v>34.41628504383247</v>
+      </c>
+      <c r="E158" t="n">
+        <v>36.44465833854805</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.5174516753152434</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>43.46618524387073</v>
+      </c>
+      <c r="D159" t="n">
+        <v>42.41707846996875</v>
+      </c>
+      <c r="E159" t="n">
+        <v>44.5152920177727</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0.5352683937955985</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>6.831762801367158</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6.293133083788204</v>
+      </c>
+      <c r="E160" t="n">
+        <v>7.370392518946112</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0.2748161302083079</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Romeu Zema</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3.001120963413011</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2.647496061822721</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3.3547458650033</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0.1804241834950223</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>4.023911108681355</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.638674181041872</v>
+      </c>
+      <c r="E162" t="n">
+        <v>4.409148036320838</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0.1965530645859734</v>
       </c>
     </row>
   </sheetData>
@@ -3912,7 +4022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q167"/>
+  <dimension ref="A1:Q172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15942,6 +16052,376 @@
         <is>
           <t>Com Flávio</t>
         </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="M168" t="n">
+        <v>33</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="P168" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Lula</t>
+        </is>
+      </c>
+      <c r="M169" t="n">
+        <v>40</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
+        </is>
+      </c>
+      <c r="M170" t="n">
+        <v>9</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Romeu Zema</t>
+        </is>
+      </c>
+      <c r="M171" t="n">
+        <v>2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>1</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
+        </is>
+      </c>
+      <c r="M172" t="n">
+        <v>7</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -16000,17 +16480,17 @@
         <v>46028</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest</t>
+          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest, Real Time Big Data</t>
         </is>
       </c>
     </row>
@@ -16024,17 +16504,17 @@
         <v>46028</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest</t>
+          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest, Real Time Big Data</t>
         </is>
       </c>
     </row>
@@ -16048,17 +16528,17 @@
         <v>46028</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest</t>
+          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest, Real Time Big Data</t>
         </is>
       </c>
     </row>
@@ -16072,17 +16552,17 @@
         <v>46028</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest</t>
+          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest, Real Time Big Data</t>
         </is>
       </c>
     </row>
@@ -16096,17 +16576,17 @@
         <v>46028</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>46216</v>
+        <v>46224</v>
       </c>
       <c r="D6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest</t>
+          <t>Atlas, Ideia, Paraná Pesquisas, PoderData, Quaest, Real Time Big Data</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V141"/>
+  <dimension ref="A1:V145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24288,18 +24768,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Quaest</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>tracking</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>semanal</t>
-        </is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>95</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -24313,7 +24802,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Com Flávio</t>
+          <t>Cenário estimulado</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -24341,17 +24830,20 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="P100" t="n">
+        <v>2004</v>
+      </c>
       <c r="Q100" t="n">
-        <v>43.3</v>
+        <v>39</v>
       </c>
       <c r="R100" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="S100" t="n">
-        <v>52.2</v>
+        <v>39</v>
       </c>
       <c r="T100" t="n">
-        <v>2.1</v>
+        <v>19</v>
       </c>
       <c r="U100" t="inlineStr">
         <is>
@@ -24359,7 +24851,7 @@
         </is>
       </c>
       <c r="V100" t="n">
-        <v>0.8686567164179104</v>
+        <v>0.6925373134328359</v>
       </c>
     </row>
     <row r="101">
@@ -24368,27 +24860,18 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Quaest</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>tracking</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>pontual</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2</v>
-      </c>
-      <c r="G101" t="n">
-        <v>95</v>
+          <t>semanal</t>
+        </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -24402,7 +24885,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Cenário estimulado</t>
+          <t>Com Flávio</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -24430,20 +24913,17 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="P101" t="n">
-        <v>2004</v>
-      </c>
       <c r="Q101" t="n">
-        <v>39</v>
+        <v>43.3</v>
       </c>
       <c r="R101" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="S101" t="n">
-        <v>39</v>
+        <v>52.2</v>
       </c>
       <c r="T101" t="n">
-        <v>19</v>
+        <v>2.1</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -24451,7 +24931,7 @@
         </is>
       </c>
       <c r="V101" t="n">
-        <v>0.6925373134328359</v>
+        <v>0.8686567164179104</v>
       </c>
     </row>
     <row r="102">
@@ -26098,7 +26578,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Cenário 3</t>
+          <t>Cenário 2</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -26130,16 +26610,16 @@
         <v>4999</v>
       </c>
       <c r="Q121" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="R121" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="S121" t="n">
-        <v>37.7</v>
+        <v>43.7</v>
       </c>
       <c r="T121" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -26190,7 +26670,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Cenário 2</t>
+          <t>Cenário 1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -26222,16 +26702,16 @@
         <v>4999</v>
       </c>
       <c r="Q122" t="n">
-        <v>47.2</v>
+        <v>46.3</v>
       </c>
       <c r="R122" t="n">
         <v>7.8</v>
       </c>
       <c r="S122" t="n">
-        <v>43.7</v>
+        <v>44.7</v>
       </c>
       <c r="T122" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -26282,7 +26762,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Cenário 1</t>
+          <t>Cenário 3</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -26314,16 +26794,16 @@
         <v>4999</v>
       </c>
       <c r="Q123" t="n">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
       <c r="R123" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="S123" t="n">
-        <v>44.7</v>
+        <v>37.7</v>
       </c>
       <c r="T123" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -26374,7 +26854,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Cenário 2</t>
+          <t>Cenário 3</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -26406,16 +26886,16 @@
         <v>4999</v>
       </c>
       <c r="Q124" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="R124" t="n">
-        <v>3</v>
+        <v>8.6</v>
       </c>
       <c r="S124" t="n">
-        <v>48.5</v>
+        <v>37.2</v>
       </c>
       <c r="T124" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -26466,7 +26946,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Cenário 1</t>
+          <t>Cenário 2</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -26498,16 +26978,16 @@
         <v>4999</v>
       </c>
       <c r="Q125" t="n">
-        <v>46.3</v>
+        <v>47.2</v>
       </c>
       <c r="R125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S125" t="n">
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="T125" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -26558,7 +27038,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Cenário 3</t>
+          <t>Cenário 1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -26590,16 +27070,16 @@
         <v>4999</v>
       </c>
       <c r="Q126" t="n">
-        <v>47.1</v>
+        <v>46.3</v>
       </c>
       <c r="R126" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="S126" t="n">
-        <v>37.2</v>
+        <v>50.5</v>
       </c>
       <c r="T126" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="U126" t="inlineStr">
         <is>
@@ -26650,7 +27130,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Cenário 3</t>
+          <t>Cenário 1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -26682,16 +27162,16 @@
         <v>4999</v>
       </c>
       <c r="Q127" t="n">
-        <v>47.1</v>
+        <v>46.3</v>
       </c>
       <c r="R127" t="n">
-        <v>8.1</v>
+        <v>2.9</v>
       </c>
       <c r="S127" t="n">
-        <v>37.7</v>
+        <v>49.6</v>
       </c>
       <c r="T127" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -26742,7 +27222,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Cenário 1</t>
+          <t>Cenário 3</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -26774,16 +27254,16 @@
         <v>4999</v>
       </c>
       <c r="Q128" t="n">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
       <c r="R128" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="S128" t="n">
-        <v>49.6</v>
+        <v>37.7</v>
       </c>
       <c r="T128" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -27892,6 +28372,362 @@
       </c>
       <c r="V141" t="n">
         <v>0.8686567164179104</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>95</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Flávio</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>40</v>
+      </c>
+      <c r="R142" t="n">
+        <v>33</v>
+      </c>
+      <c r="S142" t="n">
+        <v>27</v>
+      </c>
+      <c r="T142" t="n">
+        <v>6</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="V142" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2</v>
+      </c>
+      <c r="G143" t="n">
+        <v>95</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Renan Santos</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>40</v>
+      </c>
+      <c r="R143" t="n">
+        <v>9</v>
+      </c>
+      <c r="S143" t="n">
+        <v>51</v>
+      </c>
+      <c r="T143" t="n">
+        <v>6</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="V143" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" t="n">
+        <v>95</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Romeu Zema</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>40</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2</v>
+      </c>
+      <c r="S144" t="n">
+        <v>58</v>
+      </c>
+      <c r="T144" t="n">
+        <v>6</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="V144" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Real Time Big Data</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>pontual</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F145" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" t="n">
+        <v>95</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>1º turno</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Estimulada</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Ronaldo Caiado</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>40</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7</v>
+      </c>
+      <c r="S145" t="n">
+        <v>53</v>
+      </c>
+      <c r="T145" t="n">
+        <v>6</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Totais</t>
+        </is>
+      </c>
+      <c r="V145" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
